--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/InvestmentInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/InvestmentInfo001.xlsx
@@ -16,7 +16,7 @@
     <sheet name="接口数据要求" sheetId="3" r:id="rId2"/>
     <sheet name="报表影响点" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -114,7 +114,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>占总份额比例*</t>
+    <t>占总份额比例(%)*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -279,6 +279,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -316,7 +321,7 @@
         <xdr:cNvPr id="2" name="图片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4546FE02-E43C-CE54-6251-41CE5B80DD19}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4546FE02-E43C-CE54-6251-41CE5B80DD19}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -616,8 +621,8 @@
     <col min="3" max="3" width="14.75" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="20.25" customWidth="1"/>
-    <col min="6" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="6" max="6" width="20.625" style="18" customWidth="1"/>
+    <col min="7" max="7" width="23" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -636,10 +641,10 @@
       <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="16" t="s">
         <v>22</v>
       </c>
     </row>
@@ -649,8 +654,8 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
@@ -658,8 +663,8 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
@@ -667,8 +672,8 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
@@ -676,8 +681,8 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
@@ -685,8 +690,8 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
@@ -694,8 +699,8 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/InvestmentInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/InvestmentInfo001.xlsx
@@ -12,9 +12,7 @@
     <workbookView xWindow="5310" yWindow="1725" windowWidth="19500" windowHeight="11730"/>
   </bookViews>
   <sheets>
-    <sheet name="接口数据" sheetId="1" r:id="rId1"/>
-    <sheet name="接口数据要求" sheetId="3" r:id="rId2"/>
-    <sheet name="报表影响点" sheetId="2" r:id="rId3"/>
+    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,78 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>持有份额</t>
-  </si>
-  <si>
-    <t>占总份额比例</t>
-  </si>
-  <si>
-    <t>产品主代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类别</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>联合主键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只接非指数现管类产品的产品主代码；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枚举值：01:个人；02：机构；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枚举值：01:半年报；02：年报；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小数；最多保留两位小数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小数；最多保留四位小数，因为前台要展示xx.xx%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>年度*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据类型*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>排名*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -106,15 +38,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>类别*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>持有份额*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>占总份额比例(%)*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指标类型(01半年度/01年度)*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类别(01个人/02机构)*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -122,7 +58,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,39 +80,8 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,14 +94,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -219,71 +118,27 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -299,55 +154,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>192865</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>21893</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4546FE02-E43C-CE54-6251-41CE5B80DD19}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1432560" y="0"/>
-          <a:ext cx="11561905" cy="7733333"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -616,36 +422,36 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.375" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
     <col min="3" max="3" width="14.75" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="20.25" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="18" customWidth="1"/>
-    <col min="7" max="7" width="23" style="18" customWidth="1"/>
+    <col min="5" max="5" width="25.375" customWidth="1"/>
+    <col min="6" max="6" width="20.625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="23" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>19</v>
+    <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -654,8 +460,8 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
@@ -663,8 +469,8 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
@@ -672,8 +478,8 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
@@ -681,8 +487,8 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
@@ -690,8 +496,8 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
@@ -699,124 +505,12 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="21.75" customWidth="1"/>
-    <col min="2" max="2" width="34.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="15"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="15"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="15"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B7" s="5"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B8" s="5"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:B5"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/InvestmentInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/InvestmentInfo001.xlsx
@@ -46,11 +46,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指标类型(01半年度/01年度)*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类别(01个人/02机构)*</t>
+    <t>类别*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指标类型*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -103,42 +103,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -427,89 +413,91 @@
     <col min="3" max="3" width="14.75" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="25.375" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="23" style="6" customWidth="1"/>
+    <col min="6" max="6" width="20.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>5</v>
+      <c r="B1" s="8" t="s">
+        <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="A2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"年报,半年报"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
+      <formula1>"个人,机构"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/InvestmentInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/InvestmentInfo001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IdeaProjects\tams-njyh\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,13 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>年度*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排名*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -107,14 +103,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -405,88 +398,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
     <col min="2" max="2" width="28.25" customWidth="1"/>
-    <col min="3" max="3" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="25.375" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="25.375" customWidth="1"/>
+    <col min="5" max="5" width="20.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="6"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="F7" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -494,7 +477,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
       <formula1>"年报,半年报"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"个人,机构"</formula1>
     </dataValidation>
   </dataValidations>
